--- a/tools/importer/reports/import-pc-landing-page.report.xlsx
+++ b/tools/importer/reports/import-pc-landing-page.report.xlsx
@@ -61,7 +61,7 @@
     <t>pc-landing-page</t>
   </si>
   <si>
-    <t>2026-03-23T15:44:07.859Z</t>
+    <t>2026-03-23T16:26:13.306Z</t>
   </si>
   <si>
     <t>Dell AI Laptops &amp; PCs with Intel Processors | Dell USA</t>
@@ -100,7 +100,7 @@
     <t>en-us/lp/dell-pro-max-pcs</t>
   </si>
   <si>
-    <t>2026-03-23T15:44:13.394Z</t>
+    <t>2026-03-23T16:26:20.875Z</t>
   </si>
   <si>
     <t>Dell Pro Max High-Performance PCs, Laptops &amp; Desktops | Dell USA</t>

--- a/tools/importer/reports/import-pc-landing-page.report.xlsx
+++ b/tools/importer/reports/import-pc-landing-page.report.xlsx
@@ -61,7 +61,7 @@
     <t>pc-landing-page</t>
   </si>
   <si>
-    <t>2026-03-23T16:26:13.306Z</t>
+    <t>2026-03-23T16:51:16.965Z</t>
   </si>
   <si>
     <t>Dell AI Laptops &amp; PCs with Intel Processors | Dell USA</t>
@@ -100,7 +100,7 @@
     <t>en-us/lp/dell-pro-max-pcs</t>
   </si>
   <si>
-    <t>2026-03-23T16:26:20.875Z</t>
+    <t>2026-03-23T16:51:23.302Z</t>
   </si>
   <si>
     <t>Dell Pro Max High-Performance PCs, Laptops &amp; Desktops | Dell USA</t>

--- a/tools/importer/reports/import-pc-landing-page.report.xlsx
+++ b/tools/importer/reports/import-pc-landing-page.report.xlsx
@@ -46,7 +46,7 @@
     <t>en-us/lp/aipc.report.json</t>
   </si>
   <si>
-    <t>["hero","hero","hero","hero","hero","columns","columns","cards","cards","cards","cards","cards","cards","accordion","accordion"]</t>
+    <t>["agreements","agreements","hero","hero","hero","hero","hero","columns","columns","cards","cards","cards","cards","cards","cards","accordion","accordion"]</t>
   </si>
   <si>
     <t/>
@@ -61,7 +61,7 @@
     <t>pc-landing-page</t>
   </si>
   <si>
-    <t>2026-03-23T16:51:16.965Z</t>
+    <t>2026-03-24T15:54:14.087Z</t>
   </si>
   <si>
     <t>Dell AI Laptops &amp; PCs with Intel Processors | Dell USA</t>
@@ -94,13 +94,13 @@
     <t>en-us/lp/dell-pro-max-pcs.report.json</t>
   </si>
   <si>
-    <t>["hero","columns","columns","cards","cards","accordion"]</t>
+    <t>["agreements","agreements","hero","showcase","showcase","showcase","columns","columns","cards","cards","accordion"]</t>
   </si>
   <si>
     <t>en-us/lp/dell-pro-max-pcs</t>
   </si>
   <si>
-    <t>2026-03-23T16:51:23.302Z</t>
+    <t>2026-03-24T15:54:22.184Z</t>
   </si>
   <si>
     <t>Dell Pro Max High-Performance PCs, Laptops &amp; Desktops | Dell USA</t>
